--- a/output/pdf_financials_xlsx/KDK.xlsx
+++ b/output/pdf_financials_xlsx/KDK.xlsx
@@ -5584,31 +5584,31 @@
         <v>4.082791</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.942824</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.416209</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.400821</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.546547</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.445602</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.810946</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.560204000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.214288</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.766249</v>
       </c>
     </row>
     <row r="93">
@@ -9458,7 +9458,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11898,7 +11902,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13784,7 +13792,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KDK.xlsx
+++ b/output/pdf_financials_xlsx/KDK.xlsx
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.244069</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.138638</v>
       </c>
     </row>
     <row r="13">
@@ -1930,10 +1930,10 @@
         <v>-2.690975</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.937011</v>
+        <v>-4.18108</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.52534</v>
+        <v>-1.663978</v>
       </c>
     </row>
     <row r="28">
@@ -2040,10 +2040,10 @@
         <v>-2.690975</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.937011</v>
+        <v>-4.18108</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.52534</v>
+        <v>-1.663978</v>
       </c>
     </row>
     <row r="30">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09675</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>3.140756</v>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09675</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>3.140756</v>
@@ -17554,7 +17554,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -40276,7 +40276,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
